--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4952,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0.096858</v>
+        <v>0.100129</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0.10488</v>
+        <v>0.103456</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.09376900000000001</v>
+        <v>0.100151</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0.111821</v>
+        <v>0.106088</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0.09199400000000001</v>
+        <v>0.097651</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0.08795699999999999</v>
+        <v>0.09501800000000001</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0.083116</v>
+        <v>0.090868</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0.08885700000000001</v>
+        <v>0.095753</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0.09626800000000001</v>
+        <v>0.099231</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0.094051</v>
+        <v>0.095429</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>0.142065</v>
+        <v>0.119179</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0.127736</v>
+        <v>0.112328</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0.209401</v>
+        <v>0.103644</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -5812,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0.095792</v>
+        <v>0.09687</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>0.08966200000000001</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0.218151</v>
+        <v>0.212222</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0.329161</v>
+        <v>0.314089</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6027,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.122395</v>
+        <v>0.108502</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0.103935</v>
+        <v>0.102065</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0.093456</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>1</v>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0.083608</v>
+        <v>0.092302</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>0.09259100000000001</v>
+        <v>0.09604500000000001</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0.094114</v>
+        <v>0.09719800000000001</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0.204641</v>
+        <v>0.205209</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0.09180199999999999</v>
+        <v>0.096344</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0.175596</v>
+        <v>0.189932</v>
       </c>
       <c r="J144" t="n">
         <v>1</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0.305868</v>
+        <v>0.302357</v>
       </c>
       <c r="J146" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>0.095386</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0.09365999999999999</v>
+        <v>0.095544</v>
       </c>
       <c r="J149" t="n">
         <v>1</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0.182531</v>
+        <v>0.193852</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
@@ -6973,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0.300601</v>
+        <v>0.301612</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0.095586</v>
+        <v>0.098083</v>
       </c>
       <c r="J153" t="n">
         <v>1</v>
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0.396038</v>
+        <v>0.397434</v>
       </c>
       <c r="J154" t="n">
         <v>1</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0.093656</v>
+        <v>0.09578399999999999</v>
       </c>
       <c r="J156" t="n">
         <v>1</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>0.09845</v>
       </c>
       <c r="J157" t="n">
         <v>1</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0.09229</v>
+        <v>0.095264</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -7274,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>0.098707</v>
+        <v>0.098097</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0.276963</v>
+        <v>0.288132</v>
       </c>
       <c r="J164" t="n">
         <v>1</v>
@@ -7575,7 +7575,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0.177374</v>
+        <v>0.093499</v>
       </c>
       <c r="J166" t="n">
         <v>1</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>0.09456100000000001</v>
       </c>
       <c r="J167" t="n">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0.20099</v>
+        <v>0.19642</v>
       </c>
       <c r="J168" t="n">
         <v>1</v>
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>0.216398</v>
+        <v>0.3044</v>
       </c>
       <c r="J169" t="n">
         <v>1</v>
@@ -7790,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0.107016</v>
+        <v>0.10289</v>
       </c>
       <c r="J171" t="n">
         <v>1</v>
@@ -7833,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0.334104</v>
+        <v>0.311785</v>
       </c>
       <c r="J172" t="n">
         <v>1</v>
@@ -7876,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>0.08519400000000001</v>
+        <v>0.09279800000000001</v>
       </c>
       <c r="J173" t="n">
         <v>1</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>0.079656</v>
+        <v>0.088323</v>
       </c>
       <c r="J186" t="n">
         <v>1</v>
@@ -8521,7 +8521,7 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>0.18908</v>
+        <v>0.097209</v>
       </c>
       <c r="J188" t="n">
         <v>1</v>
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0.300798</v>
+        <v>0.210379</v>
       </c>
       <c r="J189" t="n">
         <v>1</v>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0.315558</v>
+        <v>0.308498</v>
       </c>
       <c r="J190" t="n">
         <v>1</v>
@@ -8650,7 +8650,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>0.203699</v>
+        <v>0.201372</v>
       </c>
       <c r="J191" t="n">
         <v>1</v>
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>0.28411</v>
+        <v>0.487139</v>
       </c>
       <c r="J192" t="n">
         <v>1</v>
@@ -8736,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0.233468</v>
+        <v>0.210737</v>
       </c>
       <c r="J193" t="n">
         <v>1</v>
@@ -8779,7 +8779,7 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0.295904</v>
+        <v>0.294395</v>
       </c>
       <c r="J194" t="n">
         <v>1</v>
@@ -8822,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>0.090785</v>
+        <v>0.095375</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0.194438</v>
+        <v>0.19656</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>0.30666</v>
+        <v>0.307462</v>
       </c>
       <c r="J197" t="n">
         <v>1</v>
@@ -8951,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>0.312389</v>
+        <v>0.40068</v>
       </c>
       <c r="J198" t="n">
         <v>1</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0.297661</v>
+        <v>0.298791</v>
       </c>
       <c r="J199" t="n">
         <v>1</v>
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>0.097444</v>
+        <v>0.101732</v>
       </c>
       <c r="J200" t="n">
         <v>1</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>0.199182</v>
+        <v>0.199782</v>
       </c>
       <c r="J201" t="n">
         <v>1</v>
